--- a/3.xlsx
+++ b/3.xlsx
@@ -884,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,6 +936,21 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
         </is>
       </c>
     </row>
@@ -954,6 +969,9 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -970,6 +988,9 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -986,6 +1007,9 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1002,6 +1026,9 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1040,6 +1067,9 @@
           <t>فلتر هوا (كمية 1)</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1078,6 +1108,9 @@
           <t>فلتر هوا (كمية 1)</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1114,6 +1147,60 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>فلتر زيت (كمية 1)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chillers</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>تلف</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>استبدال</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>حماده</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>رولمان بلي (كمية 1)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>غير ملتزم</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1338,7 @@
         <v>6006</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>

--- a/3.xlsx
+++ b/3.xlsx
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,31 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>مده الاصلاح</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>قطع غيار مستخدمة</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>نوع العطل</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>قدرة الفني (حل/تفكير/مبادرة/قرار)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>الالتزام بتعليمات السلامة</t>
         </is>
       </c>
     </row>
@@ -830,6 +855,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -844,6 +874,11 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -858,6 +893,11 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -872,6 +912,58 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Conveyors</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>شد سيور</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>علي</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>غير ملتزم</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3.xlsx
+++ b/3.xlsx
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,6 +962,53 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>غير ملتزم</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Conveyors</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>صيانه</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>تنظيف البورده</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>علي</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>إلكتروني</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ملتزم جزئياً</t>
         </is>
       </c>
     </row>

--- a/3.xlsx
+++ b/3.xlsx
@@ -1425,7 +1425,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>21</v>

--- a/3.xlsx
+++ b/3.xlsx
@@ -21,9 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,9 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +505,11 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>الالتزام بتعليمات السلامة</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>رابط الصورة</t>
         </is>
       </c>
     </row>
@@ -523,6 +531,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -542,6 +551,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -561,6 +571,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -580,6 +591,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -621,6 +633,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -662,6 +675,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -713,6 +727,7 @@
           <t>ملتزم جزئياً</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -760,6 +775,55 @@
           <t>ملتزم بالكامل</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ugolini GSE 4 packages</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: 1-Check temperature &amp; pressure readings</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية '1-Check temperature &amp; pressure readings' بواسطة علي</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>علي</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1624,11 +1688,17 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="n">
-        <v>46126</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="E2" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-04-27 | تم بواسطة: علي</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
